--- a/server/src/data/point-tags/point-tags.xlsx
+++ b/server/src/data/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Values</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Values</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -764,6 +764,174 @@
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>first;first_without_name;first_with_name;municipality;registered;unique_location</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>(free text — the place's own website URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>xxx-xxx-xxxx;+x-xxx-xxx-xxxx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>addr:street</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>(free text — street address, e.g. '123 Main St')</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>addr:city</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>(free text — city or town name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>addr:state</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>(free text — state, province, or region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>addr:postcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>(free text — ZIP or postal code)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>addr:country</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>(free text — country name)</t>
         </is>
       </c>
     </row>

--- a/server/src/data/point-tags/point-tags.xlsx
+++ b/server/src/data/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>YYYY;DD/MM/YYYY</t>
+          <t>YYYY;DD/MM/YYYY;YYYYs</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>YYYY;DD/MM/YYYY</t>
+          <t>YYYY;DD/MM/YYYY;YYYYs</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>xxx-xxx-xxxx;+x-xxx-xxx-xxxx</t>
+          <t>xxx-xxx-xxxx;+x-xxx-xxx-xxxx;xxx xxx xxxx;+x xxx xxx xxxx</t>
         </is>
       </c>
     </row>
@@ -932,6 +932,54 @@
       <c r="B39" s="3" t="inlineStr">
         <is>
           <t>(free text — country name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wikidata</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Q12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wikipedia</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(free text — the exact title of that language's Wikipedia article, spaces as written, e.g. "Albert Einstein"; the header itself carries the language code, e.g. wikipedia:en for English, wikipedia:fr for French)</t>
         </is>
       </c>
     </row>

--- a/server/src/data/point-tags/point-tags.xlsx
+++ b/server/src/data/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>museum</t>
+          <t>museum;shop</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>first;first_without_name;first_with_name;municipality;registered;unique_location</t>
+          <t>first;first_without_name;first_with_name;municipality;country;registered;unique_location</t>
         </is>
       </c>
     </row>
@@ -980,6 +980,102 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>(free text — the exact title of that language's Wikipedia article, spaces as written, e.g. "Albert Einstein"; the header itself carries the language code, e.g. wikipedia:en for English, wikipedia:fr for French)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>shop_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>souvenir;ice_cream;fudge;clothing;grocery;jewelry;bookstore;toy;gift;antique;bakery;candy;hardware;pharmacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>shop_products</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(free text — specific products this shop sells, separated by ; for more than one, e.g. fudge;postcards;saltwater taffy — narrower than shop_type's broader category)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>product_or_type_notability</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(free text — which shop_type or shop_products value(s) this point's shop_historic_location claim is specifically about, separated by ; for more than one, e.g. fudge — needed when a shop has more than one shop_type/shop_products value but the historic claim only applies to one of them)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>shop_historic_location</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>first;first_without_name;first_with_name;municipality;country;registered;unique_location</t>
         </is>
       </c>
     </row>

--- a/server/src/data/point-tags/point-tags.xlsx
+++ b/server/src/data/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>museum;shop</t>
+          <t>museum;shop;food</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>first;first_without_name;first_with_name;municipality;country;registered;unique_location</t>
+          <t>first;first_without_name;first_with_name;municipality;state;country;registered;unique_location</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(free text — which shop_type or shop_products value(s) this point's shop_historic_location claim is specifically about, separated by ; for more than one, e.g. fudge — needed when a shop has more than one shop_type/shop_products value but the historic claim only applies to one of them)</t>
+          <t>(free text — which shop_type/shop_products/food_type/food_style/food_product value(s) this point's *_historic_location claim is specifically about, separated by ; for more than one, e.g. fudge — needed when a point has more than one of those tags but the historic claim only applies to one of them)</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,103 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>first;first_without_name;first_with_name;municipality;country;registered;unique_location</t>
+          <t>first;first_without_name;first_with_name;municipality;state;country;registered;unique_location</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>food_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>pub;bar;restaurant;fast_food;diner</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>food_style</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>mexican;tex_mex;mexican_american;chinese;american_chinese;japanese;sushi;pizza;new_york_style_pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>food_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>(free text — specific food items this place sells, separated by ; for more than one, e.g. hamburgers;fries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>food_historic_location</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>first;first_without_name;first_with_name;municipality;state;country;registered;unique_location</t>
         </is>
       </c>
     </row>

--- a/server/src/data/point-tags/point-tags.xlsx
+++ b/server/src/data/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>barn;house;hotel;store;apartment;office;warehouse;garage;shed;cabin;church;school;hospital;factory;restaurant;library</t>
+          <t>barn;house;hotel;store;apartment;office;warehouse;garage;shed;cabin;church;cathedral;chapel;mosque;synagogue;temple;kingdom_hall;school;hospital;factory;restaurant;library</t>
         </is>
       </c>
     </row>
@@ -1172,6 +1172,54 @@
       <c r="B59" t="inlineStr">
         <is>
           <t>first;first_without_name;first_with_name;municipality;state;country;registered;unique_location</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>(free text — the religion's full name, e.g. Christian, Muslim, Jewish, Buddhist, Hindu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>denomination</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(free text — the specific denomination's full name, e.g. Jehovah's Witnesses, Baptist, Lutheran, Sunni, Reform — Catholic/Roman Catholic and Orthodox/Greek Orthodox are each acceptable either way, the one exception to spelling out the full name)</t>
         </is>
       </c>
     </row>
